--- a/l10n_it_einvoice_out_rc/tests/data/account_invoice.xlsx
+++ b/l10n_it_einvoice_out_rc/tests/data/account_invoice.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -58,6 +58,9 @@
     <t xml:space="preserve">fiscal_position_id</t>
   </si>
   <si>
+    <t xml:space="preserve">fiscal_document_type_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">z0bug.invoice_ZI_9</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">z0bug.fiscalpos_rc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external.TD29</t>
   </si>
 </sst>
 </file>
@@ -196,7 +202,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -210,6 +216,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,7 +350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.11"/>
@@ -352,8 +362,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16351" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -394,77 +405,86 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>18</v>
+      <c r="H2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>18</v>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
